--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563462284</v>
+        <v>46157.93078000007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93078000007</v>
+        <v>46157.9315910251</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9315910251</v>
+        <v>46157.93395163684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395163684</v>
+        <v>46157.9371196685</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9371196685</v>
+        <v>46158.28212014829</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212014829</v>
+        <v>46158.29673051933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673051933</v>
+        <v>46158.29808337464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808337464</v>
+        <v>46158.33382810117</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382810117</v>
+        <v>46158.36850570757</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36850570757</v>
+        <v>46158.37282940057</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
